--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Alpha Low- Volatility 30 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Alpha Low- Volatility 30 ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="122">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Alpha Low- Volatility 30 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,15 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
   </si>
   <si>
@@ -70,15 +79,6 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
     <t>Divi's Laboratories Ltd.</t>
   </si>
   <si>
@@ -103,55 +103,130 @@
     <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Apollo Hospitals Enterprise Ltd.</t>
+  </si>
+  <si>
+    <t>INE437A01024</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
     <t>Tata Consultancy Services Ltd.</t>
   </si>
   <si>
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>Lupin Ltd.</t>
-  </si>
-  <si>
-    <t>INE326A01037</t>
-  </si>
-  <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
-  </si>
-  <si>
-    <t>Beverages</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Apollo Hospitals Enterprise Ltd.</t>
-  </si>
-  <si>
-    <t>INE437A01024</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Havells India Ltd.</t>
+  </si>
+  <si>
+    <t>INE176B01034</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Tech Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE669C01036</t>
+  </si>
+  <si>
+    <t>MRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE883A01011</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
   </si>
   <si>
     <t>Colgate - Palmolive (India) Ltd.</t>
@@ -163,25 +238,25 @@
     <t>Personal Products</t>
   </si>
   <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>Bosch Ltd.</t>
+  </si>
+  <si>
+    <t>INE323A01026</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
   </si>
   <si>
     <t>Infosys Ltd.</t>
@@ -190,19 +265,25 @@
     <t>INE009A01021</t>
   </si>
   <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE663F01032</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
   </si>
   <si>
     <t>Siemens Ltd.</t>
@@ -214,94 +295,10 @@
     <t>Electrical Equipment</t>
   </si>
   <si>
-    <t>Tech Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE669C01036</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Havells India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176B01034</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Info Edge (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Bosch Ltd.</t>
-  </si>
-  <si>
-    <t>INE323A01026</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -346,28 +343,31 @@
     <t>TREPS</t>
   </si>
   <si>
-    <t>^</t>
-  </si>
-  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t>Details of the Equity shares have been lent under Securities Lending and Borrowing as follows:-</t>
+  </si>
+  <si>
+    <t>Name of the Instrument</t>
+  </si>
+  <si>
+    <t>Colgate Palmolive (India) Ltd.</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -391,7 +391,7 @@
     <numFmt numFmtId="178" formatCode="##0.00%"/>
     <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -407,6 +407,18 @@
       <sz val="8.25"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -467,7 +479,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -553,6 +565,20 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -579,44 +605,44 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -643,17 +669,35 @@
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -750,13 +794,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -774,7 +818,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16078200"/>
+          <a:off x="666750" y="16459200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -789,13 +833,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -813,7 +857,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18935700"/>
+          <a:off x="666750" y="19316700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1147,19 +1191,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J96"/>
+  <dimension ref="B1:J98"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.285714285714285" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1247,10 +1291,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>166327.65</v>
+        <v>177215.44999999998</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9991570984585999</v>
+        <v>0.9986050516187999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1284,10 +1328,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>166327.65</v>
+        <v>177215.44999999998</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9991570984585999</v>
+        <v>0.9986050516187999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1310,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>469790</v>
+        <v>483316</v>
       </c>
       <c r="G8" s="15">
-        <v>8192.90</v>
+        <v>8971.31</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0492160755711</v>
+        <v>0.0505531288928</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1339,13 +1383,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>458257</v>
+        <v>495488</v>
       </c>
       <c r="G9" s="15">
-        <v>7452.63</v>
+        <v>8312.31</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0447691539361</v>
+        <v>0.0468396788013</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1365,16 +1409,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" s="14">
-        <v>119147</v>
+        <v>125687</v>
       </c>
       <c r="G10" s="15">
-        <v>6645.66</v>
+        <v>8310.42</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0399215546119</v>
+        <v>0.046829028694</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1397,13 +1441,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>529703</v>
+        <v>558672</v>
       </c>
       <c r="G11" s="15">
-        <v>6636.12</v>
+        <v>8077.28</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0398642462887</v>
+        <v>0.0455152900684</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1426,13 +1470,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>216703</v>
+        <v>228596</v>
       </c>
       <c r="G12" s="15">
-        <v>6223.06</v>
+        <v>7102.93</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0373829280528</v>
+        <v>0.040024849861</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1455,13 +1499,13 @@
         <v>31</v>
       </c>
       <c r="F13" s="14">
-        <v>151087</v>
+        <v>439629</v>
       </c>
       <c r="G13" s="15">
-        <v>6213.30</v>
+        <v>6682.80</v>
       </c>
       <c r="H13" s="16">
-        <v>0.037324298154</v>
+        <v>0.0376574268156</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1484,13 +1528,13 @@
         <v>34</v>
       </c>
       <c r="F14" s="14">
-        <v>1375007</v>
+        <v>120878</v>
       </c>
       <c r="G14" s="15">
-        <v>6153.16</v>
+        <v>6660.98</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0369630274458</v>
+        <v>0.0375344716092</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1510,16 +1554,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" s="14">
-        <v>293839</v>
+        <v>309950</v>
       </c>
       <c r="G15" s="15">
-        <v>6113.17</v>
+        <v>6067.89</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0367228010471</v>
+        <v>0.0341924228766</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1542,13 +1586,13 @@
         <v>39</v>
       </c>
       <c r="F16" s="14">
-        <v>416840</v>
+        <v>1450308</v>
       </c>
       <c r="G16" s="15">
-        <v>5935.80</v>
+        <v>6063.01</v>
       </c>
       <c r="H16" s="16">
-        <v>0.035657310766</v>
+        <v>0.034164924187</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1571,13 +1615,13 @@
         <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>114593</v>
+        <v>87549</v>
       </c>
       <c r="G17" s="15">
-        <v>5878.22</v>
+        <v>6023.81</v>
       </c>
       <c r="H17" s="16">
-        <v>0.035311418392</v>
+        <v>0.0339440330738</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1597,16 +1641,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>82998</v>
+        <v>477791</v>
       </c>
       <c r="G18" s="15">
-        <v>5652.58</v>
+        <v>5978.12</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0339559624128</v>
+        <v>0.0336865709575</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1617,25 +1661,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="F19" s="14">
-        <v>199620</v>
+        <v>315747</v>
       </c>
       <c r="G19" s="15">
-        <v>5632.38</v>
+        <v>5921.52</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0338346177452</v>
+        <v>0.0333676312379</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1646,25 +1690,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="F20" s="14">
-        <v>325987</v>
+        <v>230473</v>
       </c>
       <c r="G20" s="15">
-        <v>5624.74</v>
+        <v>5867.38</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0337887230294</v>
+        <v>0.0330625535627</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1687,13 +1731,13 @@
         <v>53</v>
       </c>
       <c r="F21" s="14">
-        <v>299379</v>
+        <v>343809</v>
       </c>
       <c r="G21" s="15">
-        <v>5563.96</v>
+        <v>5626.78</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0334236077377</v>
+        <v>0.0317067780058</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1713,16 +1757,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F22" s="14">
-        <v>453011</v>
+        <v>201119</v>
       </c>
       <c r="G22" s="15">
-        <v>5514.73</v>
+        <v>5592.72</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0331278751644</v>
+        <v>0.0315148506763</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1733,25 +1777,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>292309</v>
+        <v>174067</v>
       </c>
       <c r="G23" s="15">
-        <v>5494.82</v>
+        <v>5526.11</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0330082725738</v>
+        <v>0.0311395048332</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1762,25 +1806,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F24" s="14">
-        <v>218491</v>
+        <v>159383</v>
       </c>
       <c r="G24" s="15">
-        <v>5481.61</v>
+        <v>5520.07</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0329289179669</v>
+        <v>0.0311054695699</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1800,16 +1844,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>165007</v>
+        <v>47772</v>
       </c>
       <c r="G25" s="15">
-        <v>5394.24</v>
+        <v>5355.24</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0324040722441</v>
+        <v>0.0301766562488</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1832,13 +1876,13 @@
         <v>65</v>
       </c>
       <c r="F26" s="14">
-        <v>88348</v>
+        <v>345154</v>
       </c>
       <c r="G26" s="15">
-        <v>5365.68</v>
+        <v>5270.50</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0322325077043</v>
+        <v>0.0296991482659</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1858,16 +1902,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F27" s="14">
-        <v>313905</v>
+        <v>331054</v>
       </c>
       <c r="G27" s="15">
-        <v>5256.18</v>
+        <v>5210.46</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0315747234917</v>
+        <v>0.0293608242242</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1887,16 +1931,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F28" s="14">
-        <v>45287</v>
+        <v>3751</v>
       </c>
       <c r="G28" s="15">
-        <v>5202.32</v>
+        <v>5208.83</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0312511777594</v>
+        <v>0.029351639211</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1907,25 +1951,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F29" s="14">
-        <v>327256</v>
+        <v>210578</v>
       </c>
       <c r="G29" s="15">
-        <v>5125.48</v>
+        <v>5171.59</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0307895874499</v>
+        <v>0.0291417926535</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1936,25 +1980,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F30" s="14">
-        <v>56764</v>
+        <v>59883</v>
       </c>
       <c r="G30" s="15">
-        <v>5022.37</v>
+        <v>5154.13</v>
       </c>
       <c r="H30" s="16">
-        <v>0.030170189001</v>
+        <v>0.0290434059485</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1974,16 +2018,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F31" s="14">
-        <v>63327</v>
+        <v>16058</v>
       </c>
       <c r="G31" s="15">
-        <v>4891.19</v>
+        <v>5044.62</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0293821695215</v>
+        <v>0.028426319576</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1994,25 +2038,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="D32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="F32" s="14">
-        <v>190664</v>
+        <v>153018</v>
       </c>
       <c r="G32" s="15">
-        <v>4686.33</v>
+        <v>5000.78</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0281515423636</v>
+        <v>0.0281792821677</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2032,16 +2076,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F33" s="14">
-        <v>15216</v>
+        <v>308290</v>
       </c>
       <c r="G33" s="15">
-        <v>4371.43</v>
+        <v>4817.65</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0262598871259</v>
+        <v>0.0271473487607</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2052,25 +2096,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F34" s="14">
-        <v>439293</v>
+        <v>334029</v>
       </c>
       <c r="G34" s="15">
-        <v>4262.24</v>
+        <v>4768.26</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0256039651335</v>
+        <v>0.026869037228</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2090,16 +2134,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="F35" s="14">
-        <v>145066</v>
+        <v>463322</v>
       </c>
       <c r="G35" s="15">
-        <v>4227.30</v>
+        <v>4308.89</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0253940749016</v>
+        <v>0.0242804976703</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2110,25 +2154,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>90</v>
-      </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="F36" s="14">
-        <v>3555</v>
+        <v>525419</v>
       </c>
       <c r="G36" s="15">
-        <v>4039.64</v>
+        <v>4267.98</v>
       </c>
       <c r="H36" s="16">
-        <v>0.024266770926</v>
+        <v>0.0240499707458</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2139,25 +2183,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="F37" s="14">
-        <v>498169</v>
+        <v>93202</v>
       </c>
       <c r="G37" s="15">
-        <v>3850.35</v>
+        <v>3043.60</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0231296752768</v>
+        <v>0.0171506171449</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2177,16 +2221,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F38" s="14">
-        <v>137500</v>
+        <v>92306</v>
       </c>
       <c r="G38" s="15">
-        <v>224.06</v>
+        <v>2287.48</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0013459646636</v>
+        <v>0.0128898980505</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2205,25 +2249,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="H40" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>13</v>
@@ -2242,7 +2286,7 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>13</v>
@@ -2257,10 +2301,10 @@
         <v>13</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>13</v>
@@ -2294,10 +2338,10 @@
         <v>13</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>13</v>
@@ -2316,7 +2360,7 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>13</v>
@@ -2331,10 +2375,10 @@
         <v>13</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>13</v>
@@ -2353,7 +2397,7 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>13</v>
@@ -2368,10 +2412,10 @@
         <v>13</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>13</v>
@@ -2390,7 +2434,7 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>13</v>
@@ -2405,10 +2449,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>13</v>
@@ -2427,7 +2471,7 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>13</v>
@@ -2442,10 +2486,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>13</v>
@@ -2464,7 +2508,7 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>13</v>
@@ -2479,10 +2523,10 @@
         <v>13</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>13</v>
@@ -2501,7 +2545,7 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>13</v>
@@ -2516,10 +2560,10 @@
         <v>13</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>13</v>
@@ -2538,7 +2582,7 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>13</v>
@@ -2553,10 +2597,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I58" s="9" t="s">
         <v>13</v>
@@ -2575,7 +2619,7 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>13</v>
@@ -2590,10 +2634,10 @@
         <v>13</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>13</v>
@@ -2612,7 +2656,7 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>13</v>
@@ -2627,10 +2671,10 @@
         <v>13</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>13</v>
@@ -2649,7 +2693,7 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>13</v>
@@ -2664,10 +2708,10 @@
         <v>13</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I64" s="9" t="s">
         <v>13</v>
@@ -2686,7 +2730,7 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>13</v>
@@ -2701,10 +2745,10 @@
         <v>13</v>
       </c>
       <c r="G66" s="9">
-        <v>4.34</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>110</v>
+        <v>164.82</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0.0009287569712</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>13</v>
@@ -2723,7 +2767,7 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>13</v>
@@ -2738,10 +2782,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="18">
-        <v>135.97610500000883</v>
+        <v>82.73172669994528</v>
       </c>
       <c r="H68" s="19">
-        <v>0.0008168304580248288</v>
+        <v>0.0004661914083215802</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>13</v>
@@ -2752,126 +2796,136 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="18">
+        <v>177463.0017267</v>
+      </c>
+      <c r="H69" s="19">
+        <v>0.9999999999983218</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" ht="15" customHeight="1">
+      <c r="B71" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="22"/>
+    </row>
+    <row r="72" spans="2:3" ht="15" customHeight="1">
+      <c r="B72" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="18">
-        <v>166467.966105</v>
-      </c>
-      <c r="H69" s="19">
-        <v>0.9999999999986249</v>
-      </c>
-      <c r="I69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" ht="15" customHeight="1">
-      <c r="B72" s="13" t="s">
+      <c r="C72" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" ht="15" customHeight="1">
+      <c r="B73" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-    </row>
-    <row r="73" spans="2:8" ht="15" customHeight="1">
-      <c r="B73" s="13" t="s">
+      <c r="C73" s="25">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" ht="15" customHeight="1">
+      <c r="B75" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-    </row>
-    <row r="74" spans="2:8" ht="15" customHeight="1">
-      <c r="B74" s="13" t="s">
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+    </row>
+    <row r="76" spans="2:8" ht="15" customHeight="1">
+      <c r="B76" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-    </row>
-    <row r="75" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B75" s="22" t="s">
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+    </row>
+    <row r="77" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B77" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-    </row>
-    <row r="76" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B76" s="22" t="s">
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+    </row>
+    <row r="78" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B78" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-    </row>
-    <row r="77" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B77" s="22" t="s">
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+    </row>
+    <row r="79" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B79" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-    </row>
-    <row r="80" ht="15">
-      <c r="B80" s="21" t="s">
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+    </row>
+    <row r="82" ht="15">
+      <c r="B82" s="26" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="95" ht="15">
-      <c r="B95" s="21" t="s">
+    <row r="97" ht="15">
+      <c r="B97" s="26" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="96" ht="15">
-      <c r="B96" s="21" t="s">
+    <row r="98" ht="15">
+      <c r="B98" s="26" t="s">
         <v>121</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B74:H74"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
+  <mergeCells count="8">
     <mergeCell ref="B77:H77"/>
+    <mergeCell ref="B78:H78"/>
+    <mergeCell ref="B79:H79"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B76:H76"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
